--- a/data/xlsx/journal_indexing.xlsx
+++ b/data/xlsx/journal_indexing.xlsx
@@ -8,13 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles &amp; Indexing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="China journals (CSSCI · 北大核心)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Profiles &amp; Indexing'!$A$1:$K$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'China journals (CSSCI · 北大核心)'!$A$1:$G$8</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,60 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -91,50 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,2674 +413,2829 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Journal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ISSN (print / online)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Publisher / type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Journal contact / submissions</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Scopus</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Web of Science</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ERIC</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RILM</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DOAJ / open access</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Regional / other index</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>CSSCI / 北大核心</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>International Journal of Music Education (IJME)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>0255-7614 / 1744-795X</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>SAGE/ISME</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>via SAGE Track; [editor email withheld] / [editor email withheld]</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Yes — Q1 Music</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>SSCI + A&amp;HCI</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>No (subscription)</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Journal of Research in Music Education (JRME)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>0022-4294 / 1945-0095</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>SAGE/NAfME</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>jrme@iu.edu (via SAGE Track)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Yes — Q1 (SJR 1.40)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>SSCI (+A&amp;HCI)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Highest SJR in the set</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Music Education Research (MER)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>1461-3808 / 1469-9893</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Taylor &amp; Francis</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>via T&amp;F ScholarOne; ed. [editor email withheld]</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Yes — Q1 Music</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>SSCI + A&amp;HCI</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>British Journal of Music Education (BJME)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>0265-0517 / 1469-2104</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Cambridge UP</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>bjme@cambridge.org (via ScholarOne)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Yes — Q1 Music</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>SSCI + A&amp;HCI</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Research Studies in Music Education (RSME)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>1321-103X / 1834-5530</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>SAGE</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>via SAGE Track; [editor email withheld]</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Yes — Q1</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>likely</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Psychology of Music</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>0305-7356 / 1741-3087</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>SAGE/SEMPRE</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>psychologyofmusicjournal@gmail.com</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Yes — Q1 Music</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>SSCI</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>likely</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>International Journal of Community Music (IJCM)</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>1752-6299 / 1752-6302</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Intellect</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>via Pubkit; ed. [editor email withheld]</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>A&amp;HCI</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>likely</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Journal of Music, Technology &amp; Education (JMTE)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>1752-7066 / 1752-7074</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Intellect</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>editor.jmte@gmail.com (via Pubkit)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>likely</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Music-technology journal</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Journal of Music Teacher Education (JMTE)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>1057-0837 / 1945-0079</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>SAGE/NAfME</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>[editor email withheld] (via SAGE Track)</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>likely</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Teacher-education journal</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Music Educators Journal (MEJ)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>0027-4321 / 1945-0087</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>SAGE/NAfME</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>via SAGE Track (no public inbox); NAfME [editor email withheld]</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Practitioner-scholar</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Journal of General Music Education (was General Music Today)</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2752-7646 (online); old GMT 1048-3713</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>SAGE/NAfME</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>[editor email withheld] (via SAGE Track)</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Journal of Historical Research in Music Education (JHRME)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1536-6006 / 2328-2525</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>SAGE</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>[editor email withheld] (via ScholarOne)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Yes — Q2 History</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Update: Applications of Research in Music Education</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>8755-1233 / 1945-0109</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>SAGE/NAfME</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>[editor email withheld] (via SAGE Track)</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Applied/translational</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Journal of Quantitative Research in Music Education (JQRME)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>none yet</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>new (founding ed. Russell)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>[editor email withheld] (new; no journal site yet)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Brand-new; not yet indexed</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Action, Criticism &amp; Theory for Music Education (ACT)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>1545-4517</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>MayDay Group</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>[editor email withheld] (editor)</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Yes — Education Q3</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Yes (OA, CC BY)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Open access, no APC</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Philosophy of Music Education Review (PMER)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>1063-5734 / 1543-3412</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Indiana UP</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>via OJS (scholarworks.iu.edu); ed. [editor email withheld]</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Yes — Q1 Music/Phil</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>International Journal of Education &amp; the Arts (IJEA)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>1529-8094</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Penn State (OA)</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>ijeaassistant@gmail.com</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Yes — Q1 (arts)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Yes (OA, CC BY-NC)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Open access</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Bulletin of the Council for Research in Music Education (CRME)</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>0010-9894 / 2162-7223</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Illinois UP</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>crme@illinois.edu (via Scholastica)</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Yes — Q1 Music</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>A&amp;HCI</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>likely</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Visions of Research in Music Education (VRME)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>1938-2065</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>UConn (OA)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>via Digital Commons Submit; ed. [editor email withheld]</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Free (not DOAJ-listed)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Free to read</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>International Journal of Research in Choral Singing (IJRCS)</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>1532-5644</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>ACDA (OA)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>ijrcs@acda.org</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Free (ROAD; not DOAJ)</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>The Choral Journal</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>0009-5028 / 2163-2170</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>ACDA</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>[editor email withheld]</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Practitioner flagship</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Journal of Music Theory Pedagogy (JMTP)</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>0891-7639 / 2994-7073</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Gail Boyd de Stwolinski Ctr.</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>via Lipscomb Digital Commons + editor web form</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Free (not DOAJ)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Specialist</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Journal of Popular Music Education (JPME)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2397-6721 / 2397-673X</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Intellect</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>jpmejournal@gmail.com (ed. assistant)</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Yes — Q1 Music</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Revista Internacional de Educación Musical (RIEM)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>2307-4841</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>SAGE/ISME (OA)</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>revistariem@isme.org (via OJS)</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>No / uncertain</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>Yes (OA, no APC)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>Spanish; ISME-funded</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Finnish Journal of Music Education (FJME / Musiikkikasvatus)</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>1239-3908 / 2342-1150</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Uniarts Helsinki (OA)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>fjme@uniarts.fi</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>No / uncertain</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>none / uncertain</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>Free (DOAJ unconfirmed)</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Finnish/English</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Australian Journal of Music Education (AJME)</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>0004-9484</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>ASME</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>publications@asme.edu.au</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Informit (AU)</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Member access</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Nordic Research in Music Education (NRME)</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2703-8041 (online)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>NMH/NNRME (OA)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>via OJS at nrme.no (no email published)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Yes (OA, CC BY)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>ERIH PLUS; Norwegian Register L1</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Canadian Music Educator</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0008-4549</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>CMEA</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>research@cmea.ca (also journal@cmea.ca)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>ProQuest</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Member access</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Revista Electrónica Complutense de Inv. en Educación Musical (RECIEM)</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>1698-7454 (online)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Univ. Complutense Madrid (OA)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>[editor email withheld] (via OJS)</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Yes — Q1 Music</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>ESCI (+JCR)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>Yes (diamond OA)</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Dialnet, Latindex, ERIH PLUS, REDIB, FECYT, CIRC, MIAR</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Best-indexed Spanish title</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Revista Electrónica de LEEME</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>1575-9563 (online)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Univ. de València (OA)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>leeme@uv.es (via OJS)</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Discontinued in Scopus 2025 (was Q1)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>No (likely)</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>ERIH PLUS, Dialnet, Latindex, CARHUS+, EBSCO</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Was Scopus Q1 2021-24</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Revista da ABEM</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2358-033X (online)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>ABEM, Brazil (OA)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>revistaabem@abemeducacaomusical.com.br (via OJS)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Yes (OA, CC BY)</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Latindex; CAPES Qualis A1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>El Oído Pensante</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2250-7116 (online)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Univ. de Buenos Aires (OA)</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>eloidopensante@gmail.com (via OJS)</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Yes — Q2</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>ESCI</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>Yes (OA)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Dialnet, Latindex, ERIH PLUS, Norwegian Register</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>Ethnomusicology/ed</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Mousikopaidagogika / Musical Pedagogics</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>1790-1618 (uncertain)</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Greek Society for Music Ed.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>info@eeme.gr</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>Free (not DOAJ)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>Greek/English</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Korean Journal of Research in Music Education (KJRME)</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>1229-4179 / 2713-3788</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Korean Music Ed. Society</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>editor@kmes.or.kr</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Yes — Q2 Music (from 2019/2022)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>none / uncertain</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>KCI (Korea Citation Index)</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Malaysian Journal of Music (MJM)</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>2600-9366 / 2600-9331</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>UPSI Press, Malaysia (OA)</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>mjm@fmsp.upsi.edu.my</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Yes — Q3 (since 2016)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>ESCI (since 2017)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>Yes (OA, CC BY)</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>MyCite/MyJurnal; ASEAN Citation Index</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Japanese Journal of Music Education Research (JASME)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>1880-9901 / 2424-2071</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Japan Music Ed. Society</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>onkyoiku@remus.dti.ne.jp (society office)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Free (J-STAGE)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>J-STAGE; CiNii (likely)</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Asia-Pacific Journal for Arts Education (APJAE)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Education Univ. of Hong Kong</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>cca@eduhk.hk (EdUHK CCA dept.)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>OA online</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Arts education; ISSN not found</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>China Music Education / Zhongguo Yinyue Jiaoyu</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>CN 11-2543/J</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>People's Music Pub. House</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>zgyyjy@vip.sohu.com (practitioner)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>No (subscription)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>CNKI full-text only — NOT in CSSCI/Peking Core</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>Practitioner periodical</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Music Research / Yinyue Yanjiu (音乐研究)</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>0512-7939 / CN 11-1665/J</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>People's Music Publishing House (China)</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>yyyj@rymusic.com.cn (or online platform)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>No (subscription)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>CSSCI + 北大核心 (Peking Core); SCD; CNKI</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Leading Chinese musicology research journal; carries a 音乐教育 (music education) column; founded 1958, bimonthly, Chinese. No known integrity concerns (slot-selling/paper mills).</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Music Education International (CEASED)</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>ISME</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>— (defunct; merged into IJME)</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>n/a — defunct</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>ISME's short-lived 'Practice' annual (2002-2003, Vol. 1-2), companion to IJME; ed. Wendy L. Sims; merged back into IJME c.2004. Not a current/standalone journal.</t>
         </is>
       </c>
     </row>
-  </sheetData>
-  <autoFilter ref="A1:K41"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="104" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Coverage</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Indexing as of June 2026 from Scopus/Scimago, Web of Science Master Journal List, DOAJ, ERIC, RILM, and journals' own A&amp;I pages. 'uncertain' = could not confirm on an authoritative page (database pages are often JS-gated); 'likely' = strong indirect evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>WoS tiers</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>SSCI/A&amp;HCI = core collections with an impact metric; ESCI = Emerging Sources Citation Index (in WoS, no Journal Impact Factor). Flagship dual-indexed (SSCI+A&amp;HCI): IJME, MER, BJME (JRME primarily SSCI). A&amp;HCI: IJCM, CRME.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Scopus quartiles</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>A journal can be Q1 in Music but Q2-Q3 in Education — quartile shown is the strongest category where known. Verify exact figures on the live Scimago/MJL record before publication-grade use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Open access</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Formally DOAJ-listed OA: ACT, IJEA, RIEM, RECIEM, Revista da ABEM, El Oído Pensante, NRME, MJM. Free-to-read but not DOAJ-listed: VRME, IJRCS, JMTP, FJME, JASME, Musical Pedagogics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Corrections worth noting</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>LEEME was Scopus Q1 but was DISCONTINUED in Scopus in 2025 (still ERIH PLUS/Dialnet/Latindex). China Music Education is NOT in CSSCI/Peking Core despite broker-site claims — CNKI full-text only. JQRME is brand-new and not yet indexed anywhere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Items to spot-check</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>RILM line-item coverage for several SAGE/Intellect/OA titles; ERIC for the Intellect/ACDA titles; APJAE and Musical Pedagogics ISSNs; KJRME's WoS/DOAJ/RILM status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>China journals tab</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Reference list of CSSCI / 北大核心 (Peking Core) Chinese music journals relevant to music-education research. No CSSCI/Peking-Core journal is exclusively dedicated to music education; these are general music journals, most carrying a 音乐教育 column. Integrity flags ('⚠ reported slot-selling / paper mills') reflect community report, not a verified finding — included as due-diligence guidance. 《音乐研究》is the recommended venue; dedicated music-ed titles (中国音乐教育, 中小学音乐教育) are practitioner periodicals, not indexed.</t>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Journal of the Association for Technology in Music Instruction (JATMI)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ATMI / Univ. of Tennessee (open access)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>via ATMI submit portal (atmimusic.com/jatmi)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Yes (open access)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Music-technology instruction; peer-reviewed; no formal external indexing</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>College Music Symposium</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0069-5696 / 2334-203X</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>The College Music Society</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>via symposium.music.org (submissions)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>likely</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>JSTOR (archive)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Refereed journal of the college music profession since 1961; ethics per COPE/CMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>《音乐研究》 · Music Research</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>People's Music Publishing House (人民音乐出版社)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>CNKI</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>CSSCI; 北大核心</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Tier: RECOMMENDED; Music-ed column: Yes — music-ed section</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>《中国音乐》 · Chinese Music</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>China Conservatory of Music (中国音乐学院)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>CNKI</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>CSSCI; 北大核心</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Tier: Indexed; Music-ed column: Yes — 音乐教育 regular column</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>《中央音乐学院学报》 · Journal of the Central Conservatory of Music</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Central Conservatory of Music (中央音乐学院)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>CNKI</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>CSSCI; 北大核心</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Tier: Indexed; Music-ed column: Music-ed appears at times</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>《中国音乐学》 · Musicology in China</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chinese National Academy of Arts</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>CNKI</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>CSSCI; 北大核心</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Tier: Use with caution; Music-ed column: —</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>《人民音乐》 · People's Music</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>People's Music Publishing House / Chinese Musicians Assoc.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>CNKI</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>(indexed)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Tier: Use with caution; Music-ed column: —</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>《中国音乐教育》 · China Music Education</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>People's Music Publishing House</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>CNKI</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Tier: Not indexed; Music-ed column: Yes — dedicated music-ed title</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>《中小学音乐教育》 · Primary &amp; Secondary School Music Education</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>(Zhejiang) — practitioner</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>CNKI</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Tier: Not indexed; Music-ed column: Yes — dedicated music-ed title</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Journal (中文 · English)</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Publisher / institution</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CSSCI</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>北大核心 (Peking Core)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Music-education column?</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>《音乐研究》 · Music Research</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>People's Music Publishing House (人民音乐出版社)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Yes (+ SCD)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Yes — music-ed section</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>RECOMMENDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>《中国音乐》 · Chinese Music</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>China Conservatory of Music (中国音乐学院)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Yes — 音乐教育 regular column</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Indexed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>《中央音乐学院学报》 · Journal of the Central Conservatory of Music</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Central Conservatory of Music (中央音乐学院)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Music-ed appears at times</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Indexed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>《中国音乐学》 · Musicology in China</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Chinese National Academy of Arts</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Use with caution</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>《人民音乐》 · People's Music</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>People's Music Publishing House / Chinese Musicians Assoc.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>(indexed)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>(historically core)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Use with caution</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>《中国音乐教育》 · China Music Education</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>People's Music Publishing House</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Yes — dedicated music-ed title</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Not indexed</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>《中小学音乐教育》 · Primary &amp; Secondary School Music Education</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>(Zhejiang) — practitioner</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Yes — dedicated music-ed title</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Not indexed</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/xlsx/journal_indexing.xlsx
+++ b/data/xlsx/journal_indexing.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiles &amp; Indexing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Profiles &amp; Indexing" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,7 +529,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -582,7 +581,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Highest SJR in the set</t>
@@ -640,7 +638,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -693,7 +690,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -746,7 +742,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -799,7 +794,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -852,7 +846,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -905,7 +898,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Music-technology journal</t>
@@ -963,7 +955,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Teacher-education journal</t>
@@ -1021,7 +1012,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Practitioner-scholar</t>
@@ -1079,7 +1069,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1132,7 +1121,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1185,7 +1173,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>Applied/translational</t>
@@ -1243,7 +1230,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Brand-new; not yet indexed</t>
@@ -1301,7 +1287,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>Open access, no APC</t>
@@ -1359,7 +1344,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1412,7 +1396,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>Open access</t>
@@ -1470,7 +1453,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1523,7 +1505,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>Free to read</t>
@@ -1581,7 +1562,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1634,7 +1614,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>Practitioner flagship</t>
@@ -1692,7 +1671,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>Specialist</t>
@@ -1750,7 +1728,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1803,7 +1780,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>Spanish; ISME-funded</t>
@@ -1861,7 +1837,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>Finnish/English</t>
@@ -1919,7 +1894,6 @@
           <t>Informit (AU)</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>Member access</t>
@@ -1977,7 +1951,6 @@
           <t>ERIH PLUS; Norwegian Register L1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2030,7 +2003,6 @@
           <t>ProQuest</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>Member access</t>
@@ -2088,7 +2060,6 @@
           <t>Dialnet, Latindex, ERIH PLUS, REDIB, FECYT, CIRC, MIAR</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>Best-indexed Spanish title</t>
@@ -2146,7 +2117,6 @@
           <t>ERIH PLUS, Dialnet, Latindex, CARHUS+, EBSCO</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>Was Scopus Q1 2021-24</t>
@@ -2204,7 +2174,6 @@
           <t>Latindex; CAPES Qualis A1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2257,7 +2226,6 @@
           <t>Dialnet, Latindex, ERIH PLUS, Norwegian Register</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>Ethnomusicology/ed</t>
@@ -2315,7 +2283,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>Greek/English</t>
@@ -2373,7 +2340,6 @@
           <t>KCI (Korea Citation Index)</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2426,7 +2392,6 @@
           <t>MyCite/MyJurnal; ASEAN Citation Index</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2479,7 +2444,6 @@
           <t>J-STAGE; CiNii (likely)</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2532,7 +2496,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>Arts education; ISSN not found</t>
@@ -2590,7 +2553,6 @@
           <t>CNKI full-text only — NOT in CSSCI/Peking Core</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>Practitioner periodical</t>
@@ -2648,7 +2610,6 @@
           <t>CSSCI + 北大核心 (Peking Core); SCD; CNKI</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>Leading Chinese musicology research journal; carries a 音乐教育 (music education) column; founded 1958, bimonthly, Chinese. No known integrity concerns (slot-selling/paper mills).</t>
@@ -2706,7 +2667,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>ISME's short-lived 'Practice' annual (2002-2003, Vol. 1-2), companion to IJME; ed. Wendy L. Sims; merged back into IJME c.2004. Not a current/standalone journal.</t>
@@ -2764,7 +2724,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>Music-technology instruction; peer-reviewed; no formal external indexing</t>
@@ -2822,7 +2781,6 @@
           <t>JSTOR (archive)</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>Refereed journal of the college music profession since 1961; ethics per COPE/CMS</t>
@@ -2832,7 +2790,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>《音乐研究》 · Music Research</t>
+          <t>Music Research (音乐研究)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2845,7 +2803,6 @@
           <t>People's Music Publishing House (人民音乐出版社)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>No</t>
@@ -2890,7 +2847,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>《中国音乐》 · Chinese Music</t>
+          <t>Chinese Music (中国音乐)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2903,7 +2860,6 @@
           <t>China Conservatory of Music (中国音乐学院)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>No</t>
@@ -2948,7 +2904,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>《中央音乐学院学报》 · Journal of the Central Conservatory of Music</t>
+          <t>Journal of the Central Conservatory of Music (中央音乐学院学报)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2961,7 +2917,6 @@
           <t>Central Conservatory of Music (中央音乐学院)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>No</t>
@@ -3006,7 +2961,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>《中国音乐学》 · Musicology in China</t>
+          <t>Musicology in China (中国音乐学)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3019,7 +2974,6 @@
           <t>Chinese National Academy of Arts</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>No</t>
@@ -3064,7 +3018,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>《人民音乐》 · People's Music</t>
+          <t>People's Music (人民音乐)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3077,7 +3031,6 @@
           <t>People's Music Publishing House / Chinese Musicians Assoc.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>No</t>
@@ -3122,7 +3075,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>《中国音乐教育》 · China Music Education</t>
+          <t>China Music Education (中国音乐教育)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3135,7 +3088,6 @@
           <t>People's Music Publishing House</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>No</t>
@@ -3180,7 +3132,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>《中小学音乐教育》 · Primary &amp; Secondary School Music Education</t>
+          <t>Primary &amp; Secondary School Music Education (中小学音乐教育)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3193,7 +3145,6 @@
           <t>(Zhejiang) — practitioner</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>No</t>

--- a/data/xlsx/journal_indexing.xlsx
+++ b/data/xlsx/journal_indexing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,6 +582,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Highest SJR in the set</t>
@@ -638,6 +640,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -690,6 +693,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -742,6 +746,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -794,6 +799,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -846,6 +852,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -898,6 +905,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Music-technology journal</t>
@@ -955,6 +963,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Teacher-education journal</t>
@@ -1012,6 +1021,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Practitioner-scholar</t>
@@ -1069,6 +1079,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1121,6 +1132,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1173,6 +1185,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>Applied/translational</t>
@@ -1230,6 +1243,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Brand-new; not yet indexed</t>
@@ -1287,6 +1301,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>Open access, no APC</t>
@@ -1344,6 +1359,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1396,6 +1412,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>Open access</t>
@@ -1453,6 +1470,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1505,6 +1523,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>Free to read</t>
@@ -1562,6 +1581,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1614,6 +1634,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>Practitioner flagship</t>
@@ -1671,6 +1692,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>Specialist</t>
@@ -1728,6 +1750,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1780,6 +1803,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>Spanish; ISME-funded</t>
@@ -1837,6 +1861,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>Finnish/English</t>
@@ -1894,6 +1919,7 @@
           <t>Informit (AU)</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>Member access</t>
@@ -1951,6 +1977,7 @@
           <t>ERIH PLUS; Norwegian Register L1</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2003,6 +2030,7 @@
           <t>ProQuest</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>Member access</t>
@@ -2060,6 +2088,7 @@
           <t>Dialnet, Latindex, ERIH PLUS, REDIB, FECYT, CIRC, MIAR</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>Best-indexed Spanish title</t>
@@ -2117,6 +2146,7 @@
           <t>ERIH PLUS, Dialnet, Latindex, CARHUS+, EBSCO</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>Was Scopus Q1 2021-24</t>
@@ -2174,6 +2204,7 @@
           <t>Latindex; CAPES Qualis A1</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2226,6 +2257,7 @@
           <t>Dialnet, Latindex, ERIH PLUS, Norwegian Register</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>Ethnomusicology/ed</t>
@@ -2283,6 +2315,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>Greek/English</t>
@@ -2340,6 +2373,7 @@
           <t>KCI (Korea Citation Index)</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2392,6 +2426,7 @@
           <t>MyCite/MyJurnal; ASEAN Citation Index</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2444,6 +2479,7 @@
           <t>J-STAGE; CiNii (likely)</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2496,6 +2532,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>Arts education; ISSN not found</t>
@@ -2505,7 +2542,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>China Music Education / Zhongguo Yinyue Jiaoyu</t>
+          <t>China Music Education (中国音乐教育)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2553,6 +2590,7 @@
           <t>CNKI full-text only — NOT in CSSCI/Peking Core</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>Practitioner periodical</t>
@@ -2562,7 +2600,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Music Research / Yinyue Yanjiu (音乐研究)</t>
+          <t>Music Research (音乐研究)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2610,6 +2648,7 @@
           <t>CSSCI + 北大核心 (Peking Core); SCD; CNKI</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>Leading Chinese musicology research journal; carries a 音乐教育 (music education) column; founded 1958, bimonthly, Chinese. No known integrity concerns (slot-selling/paper mills).</t>
@@ -2667,6 +2706,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>ISME's short-lived 'Practice' annual (2002-2003, Vol. 1-2), companion to IJME; ed. Wendy L. Sims; merged back into IJME c.2004. Not a current/standalone journal.</t>
@@ -2724,6 +2764,7 @@
           <t>—</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>Music-technology instruction; peer-reviewed; no formal external indexing</t>
@@ -2781,6 +2822,7 @@
           <t>JSTOR (archive)</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>Refereed journal of the college music profession since 1961; ethics per COPE/CMS</t>
@@ -2790,7 +2832,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Music Research (音乐研究)</t>
+          <t>Chinese Music (中国音乐)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2800,9 +2842,10 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>People's Music Publishing House (人民音乐出版社)</t>
-        </is>
-      </c>
+          <t>China Conservatory of Music (中国音乐学院)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>No</t>
@@ -2840,14 +2883,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Tier: RECOMMENDED; Music-ed column: Yes — music-ed section</t>
+          <t>Tier: Indexed; Music-ed column: Yes — 音乐教育 regular column</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chinese Music (中国音乐)</t>
+          <t>Journal of the Central Conservatory of Music (中央音乐学院学报)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2857,9 +2900,10 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Conservatory of Music (中国音乐学院)</t>
-        </is>
-      </c>
+          <t>Central Conservatory of Music (中央音乐学院)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>No</t>
@@ -2897,14 +2941,14 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Tier: Indexed; Music-ed column: Yes — 音乐教育 regular column</t>
+          <t>Tier: Indexed; Music-ed column: Music-ed appears at times</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Journal of the Central Conservatory of Music (中央音乐学院学报)</t>
+          <t>Musicology in China (中国音乐学)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2914,9 +2958,10 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Central Conservatory of Music (中央音乐学院)</t>
-        </is>
-      </c>
+          <t>Chinese National Academy of Arts</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>No</t>
@@ -2954,14 +2999,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Tier: Indexed; Music-ed column: Music-ed appears at times</t>
+          <t>Tier: Use with caution; Music-ed column: —</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Musicology in China (中国音乐学)</t>
+          <t>People's Music (人民音乐)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2971,9 +3016,10 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chinese National Academy of Arts</t>
-        </is>
-      </c>
+          <t>People's Music Publishing House / Chinese Musicians Assoc.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>No</t>
@@ -3006,7 +3052,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>CSSCI; 北大核心</t>
+          <t>(indexed)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3018,7 +3064,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>People's Music (人民音乐)</t>
+          <t>Primary &amp; Secondary School Music Education (中小学音乐教育)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3028,9 +3074,10 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>People's Music Publishing House / Chinese Musicians Assoc.</t>
-        </is>
-      </c>
+          <t>(Zhejiang) — practitioner</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>No</t>
@@ -3063,124 +3110,10 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>(indexed)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
-        <is>
-          <t>Tier: Use with caution; Music-ed column: —</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>China Music Education (中国音乐教育)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>People's Music Publishing House</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>CNKI</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Tier: Not indexed; Music-ed column: Yes — dedicated music-ed title</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Primary &amp; Secondary School Music Education (中小学音乐教育)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>(Zhejiang) — practitioner</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>CNKI</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
         <is>
           <t>Tier: Not indexed; Music-ed column: Yes — dedicated music-ed title</t>
         </is>

--- a/data/xlsx/journal_indexing.xlsx
+++ b/data/xlsx/journal_indexing.xlsx
@@ -3064,7 +3064,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Primary &amp; Secondary School Music Education (中小学音乐教育)</t>
+          <t>Primary and Secondary School Music Education (中小学音乐教育)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">

--- a/data/xlsx/journal_indexing.xlsx
+++ b/data/xlsx/journal_indexing.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yes — Q1 (SJR 1.40)</t>
+          <t>Yes — Q1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -583,11 +583,6 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Highest SJR in the set</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
